--- a/output/pdf_financials_xlsx/MML.H.xlsx
+++ b/output/pdf_financials_xlsx/MML.H.xlsx
@@ -2461,16 +2461,16 @@
         <v>16.533477</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>16.582589</v>
+        <v>17.603701</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>16.643873</v>
+        <v>17.665521</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>16.684244</v>
+        <v>17.705892</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>16.684244</v>
+        <v>17.749434</v>
       </c>
     </row>
     <row r="93">
@@ -4026,7 +4026,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -5404,7 +5408,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MML.H.xlsx
+++ b/output/pdf_financials_xlsx/MML.H.xlsx
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.751348</v>
+        <v>4.469645</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.016827</v>
+        <v>5.45762</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.330509</v>
+        <v>0.5415990000000001</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.072364</v>
+        <v>0.335176</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.029057</v>
+        <v>0.279812</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.05316</v>
+        <v>-3.771457</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.91395</v>
+        <v>-4.526843</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.297542</v>
+        <v>0.086452</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.072364</v>
+        <v>-0.335176</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.029057</v>
+        <v>-0.279812</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
         <v>0.04595</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.007446</v>
       </c>
     </row>
     <row r="35">
@@ -1222,7 +1222,7 @@
         <v>0.04595</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.007446</v>
       </c>
     </row>
     <row r="37">
@@ -1486,7 +1486,7 @@
         <v>0.01617</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.007446</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">

--- a/output/pdf_financials_xlsx/MML.H.xlsx
+++ b/output/pdf_financials_xlsx/MML.H.xlsx
@@ -766,7 +766,7 @@
         <v>-3.517657</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.56089</v>
+        <v>-0.5758219999999999</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>1.249672</v>
@@ -788,7 +788,7 @@
         <v>1.770162</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.014932</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1028,7 +1028,7 @@
         <v>-3.517657</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.56089</v>
+        <v>-0.5758219999999999</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>1.249672</v>
@@ -1072,7 +1072,7 @@
         <v>-3.515933</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.559346</v>
+        <v>-0.574278</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>1.249672</v>
@@ -1120,7 +1120,7 @@
         <v>-50.32218888879729</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.593162470346739</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.024673</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.028076</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.010156</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.06538099999999999</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008446</v>
       </c>
     </row>
     <row r="102">
@@ -2751,19 +2751,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.140972</v>
+        <v>0.116299</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.304176</v>
+        <v>-0.332252</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.322794</v>
+        <v>0.33295</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.006794</v>
+        <v>0.058587</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.038932</v>
+        <v>-0.047378</v>
       </c>
     </row>
     <row r="107">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>1.133683</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.013815</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -6134,7 +6134,11 @@
           <t>Income (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -6460,7 +6464,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>-0.024673</v>
       </c>
@@ -7084,7 +7092,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -8330,7 +8342,11 @@
           <t>Interest accretion expense</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E123" s="5" t="n">
         <v>1.133683</v>
       </c>
@@ -8829,7 +8845,11 @@
           <t>Deferred income tax recovery (note 6)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
